--- a/Facebook QA.xlsx
+++ b/Facebook QA.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="441">
   <si>
-    <t>Facebook  |  QA Test Case Suite  |  Functional · Regression · Usability  |  Tester: Md Sayem Mottakee  |  Email: sayemmottakee2000@gmail.com</t>
+    <t>Facebook  |  QA Test Case Suite  |  Functional · Regression · Usability  |  Tester: Ariful Islam  |  Email: arifulislam.ash8@gmail.com</t>
   </si>
   <si>
     <t>TC ID</t>
@@ -107,7 +107,7 @@
     <t>Go to facebook.com → Click 'Create new account' → Fill all fields with valid data → Click 'Sign Up'</t>
   </si>
   <si>
-    <t>Name: Md Sayem Mottakee | Email: sayemmottakee2000@gmail.com | DOB: 01/Jan/1995 | Pass: Test@1234!</t>
+    <t>Name: Ariful Islam | Email: arifulislam.ash8@gmail.com | DOB: 01/Jan/1995 | Pass: Test@1234!</t>
   </si>
   <si>
     <t>Account created; confirmation email sent; user lands on confirm email screen.</t>
@@ -125,7 +125,7 @@
     <t>v.2026.04</t>
   </si>
   <si>
-    <t>Md Sayem Mottakee</t>
+    <t>Ariful Islam</t>
   </si>
   <si>
     <t>2026-04-01</t>
@@ -149,7 +149,7 @@
     <t>Go to Sign Up → Enter already-registered email → Fill remaining fields → Click Sign Up</t>
   </si>
   <si>
-    <t>Email: sayemmottakee2000@gmail.com (already registered)</t>
+    <t>Email: arifulislam.ash8@gmail.com (already registered)</t>
   </si>
   <si>
     <t>Error: 'It looks like you already have an account' displayed. Registration blocked.</t>
@@ -239,7 +239,7 @@
     <t>Go to facebook.com → Enter valid email and password → Click 'Log In'</t>
   </si>
   <si>
-    <t>Email: sayemmottakee2000@gmail.com | Pass: Test@1234!</t>
+    <t>Email: arifulislam.ash8@gmail.com | Pass: Test@1234!</t>
   </si>
   <si>
     <t>User lands on News Feed. Name displayed in top nav.</t>
@@ -263,7 +263,7 @@
     <t>Go to facebook.com → Enter valid email → Enter wrong password → Click Log In</t>
   </si>
   <si>
-    <t>Email: sayemmottakee2000@gmail.com | Pass: WrongPass99</t>
+    <t>Email: arifulislam.ash8@gmail.com | Pass: WrongPass99</t>
   </si>
   <si>
     <t>Error: 'The password you've entered is incorrect.' Login denied.</t>
@@ -299,7 +299,7 @@
     <t>Attempt login with wrong password 5 times consecutively</t>
   </si>
   <si>
-    <t>Email: sayemmottakee2000@gmail.com | Wrong password repeated 5x</t>
+    <t>Email: arifulislam.ash8@gmail.com | Wrong password repeated 5x</t>
   </si>
   <si>
     <t>Lockout message displayed. CAPTCHA or cooldown enforced.</t>
@@ -332,7 +332,7 @@
     <t>Click 'Forgotten password?' → Enter email → Click Search → Click 'Send code' → Open email → Enter code → Set new password</t>
   </si>
   <si>
-    <t>Email: sayemmottakee2000@gmail.com | New pass: NewPass@5678!</t>
+    <t>Email: arifulislam.ash8@gmail.com | New pass: NewPass@5678!</t>
   </si>
   <si>
     <t>Password reset. User can log in with new password immediately.</t>
@@ -1298,7 +1298,7 @@
     <t>'Create new account' button skipped in Tab order</t>
   </si>
   <si>
-    <t>📊  Facebook QA — Execution Dashboard  |  Md Sayem Mottakee</t>
+    <t>📊  Facebook QA — Execution Dashboard  |  Ariful Islam</t>
   </si>
   <si>
     <t>Metric</t>
